--- a/inputs/data_symbols_TD/17_LTAN06_800km_1213COLD_MX_STTLCT_HEAT_MX_0p5.xlsx
+++ b/inputs/data_symbols_TD/17_LTAN06_800km_1213COLD_MX_STTLCT_HEAT_MX_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57F76A8E-AD66-45DA-8635-10E15DEC856B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08918571-CA47-4A3B-90A7-37FF47EDBBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{89E25998-B323-4808-9806-926BDF94B29B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{6E060E8D-9FB9-47DC-A808-29D2579A6C71}"/>
   </bookViews>
   <sheets>
     <sheet name="17_LTAN06_800km_1213COLD_MX_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EC7A5F-5B6C-4238-84FC-95597BAE28C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4947EADF-5EAF-4743-A779-74A48DC24F3A}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
